--- a/analises/vinhos/cotacao-60-garrafas-borgonha-agosto-2026.xlsx
+++ b/analises/vinhos/cotacao-60-garrafas-borgonha-agosto-2026.xlsx
@@ -551,10 +551,10 @@
         <v>143.49</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4">
-        <v>2152.3500000000004</v>
+        <v>4591.68</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -571,10 +571,10 @@
         <v>187.86</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4">
-        <v>2817.9</v>
+        <v>563.58</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -591,10 +591,10 @@
         <v>206.22</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4">
-        <v>2474.64</v>
+        <v>618.66</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -611,10 +611,10 @@
         <v>225.42</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4">
-        <v>2479.62</v>
+        <v>676.26</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -631,10 +631,10 @@
         <v>245.93</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4">
-        <v>245.93</v>
+        <v>737.79</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -651,10 +651,10 @@
         <v>266.35</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4">
-        <v>266.35</v>
+        <v>799.0500000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -671,10 +671,10 @@
         <v>277.32</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="4">
-        <v>277.32</v>
+        <v>831.96</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -691,10 +691,10 @@
         <v>302.43</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="4">
-        <v>302.43</v>
+        <v>907.29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -711,10 +711,10 @@
         <v>304.74</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="4">
-        <v>304.74</v>
+        <v>914.22</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>322.68</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4">
-        <v>322.68</v>
+        <v>645.36</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -751,10 +751,10 @@
         <v>343.06</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="4">
-        <v>343.06</v>
+        <v>686.12</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -774,7 +774,7 @@
         <v>60</v>
       </c>
       <c r="F15" s="7">
-        <v>11987.019999999999</v>
+        <v>11971.970000000001</v>
       </c>
     </row>
   </sheetData>

--- a/analises/vinhos/cotacao-60-garrafas-borgonha-agosto-2026.xlsx
+++ b/analises/vinhos/cotacao-60-garrafas-borgonha-agosto-2026.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
-  <si>
-    <t>Cotação — 60 garrafas · faixa R$ 10.000 a R$ 12.000 · Borgonha/Alsace</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+  <si>
+    <t>Cotação — 60 garrafas · faixa R$ 10.000 a R$ 12.000 · distribuição equilibrada</t>
   </si>
   <si>
     <t>Vinho</t>
@@ -56,36 +56,6 @@
   </si>
   <si>
     <t>R.Q.W.R. G. Riquewihr Gewurztraminer</t>
-  </si>
-  <si>
-    <t>Bourgogne Aligoté</t>
-  </si>
-  <si>
-    <t>Les Petits Lieux</t>
-  </si>
-  <si>
-    <t>Bourgogne Chardonnay</t>
-  </si>
-  <si>
-    <t>Aurore Bachelet</t>
-  </si>
-  <si>
-    <t>Hautes Côtes de Beaune "Vieilles Vignes"</t>
-  </si>
-  <si>
-    <t>Jean Chartron</t>
-  </si>
-  <si>
-    <t>Mâcon-Cruzille Clos des Avoueries Calcaire</t>
-  </si>
-  <si>
-    <t>Bourgogne Côte d'Or</t>
-  </si>
-  <si>
-    <t>Domaine Guy Bocard</t>
-  </si>
-  <si>
-    <t>Domaine Remi Jobard</t>
   </si>
   <si>
     <t/>
@@ -496,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -551,10 +521,10 @@
         <v>143.49</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4">
-        <v>4591.68</v>
+        <v>2008.8600000000001</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -571,10 +541,10 @@
         <v>187.86</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F5" s="4">
-        <v>563.58</v>
+        <v>2254.32</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -591,10 +561,10 @@
         <v>206.22</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F6" s="4">
-        <v>618.66</v>
+        <v>2474.64</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -611,10 +581,10 @@
         <v>225.42</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F7" s="4">
-        <v>676.26</v>
+        <v>2705.04</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -631,150 +601,30 @@
         <v>245.93</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F8" s="4">
-        <v>737.79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>2459.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9">
-        <v>2023</v>
-      </c>
-      <c r="D9" s="4">
-        <v>266.35</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4">
-        <v>799.0500000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10">
-        <v>2023</v>
-      </c>
-      <c r="D10" s="4">
-        <v>277.32</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10" s="4">
-        <v>831.96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>2023</v>
-      </c>
-      <c r="D11" s="4">
-        <v>302.43</v>
-      </c>
-      <c r="E11">
-        <v>3</v>
-      </c>
-      <c r="F11" s="4">
-        <v>907.29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>2022</v>
-      </c>
-      <c r="D12" s="4">
-        <v>304.74</v>
-      </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
-      <c r="F12" s="4">
-        <v>914.22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13">
-        <v>2023</v>
-      </c>
-      <c r="D13" s="4">
-        <v>322.68</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13" s="4">
-        <v>645.36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14">
-        <v>2022</v>
-      </c>
-      <c r="D14" s="4">
-        <v>343.06</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14" s="4">
-        <v>686.12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="C9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="6">
         <v>60</v>
       </c>
-      <c r="F15" s="7">
-        <v>11971.970000000001</v>
+      <c r="F9" s="7">
+        <v>11902.16</v>
       </c>
     </row>
   </sheetData>

--- a/analises/vinhos/cotacao-60-garrafas-borgonha-agosto-2026.xlsx
+++ b/analises/vinhos/cotacao-60-garrafas-borgonha-agosto-2026.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
-  <si>
-    <t>Cotação — 60 garrafas · faixa R$ 10.000 a R$ 12.000 · distribuição equilibrada</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+  <si>
+    <t>Cotação — 60 garrafas · 19 rótulos · faixa R$ 13.000 a R$ 14.000</t>
   </si>
   <si>
     <t>Vinho</t>
@@ -56,6 +56,72 @@
   </si>
   <si>
     <t>R.Q.W.R. G. Riquewihr Gewurztraminer</t>
+  </si>
+  <si>
+    <t>Bourgogne Aligoté</t>
+  </si>
+  <si>
+    <t>Les Petits Lieux</t>
+  </si>
+  <si>
+    <t>Bourgogne Chardonnay</t>
+  </si>
+  <si>
+    <t>Aurore Bachelet</t>
+  </si>
+  <si>
+    <t>Hautes Côtes de Beaune "Vieilles Vignes"</t>
+  </si>
+  <si>
+    <t>Jean Chartron</t>
+  </si>
+  <si>
+    <t>Mâcon-Cruzille Clos des Avoueries Calcaire</t>
+  </si>
+  <si>
+    <t>Bourgogne Côte d'Or</t>
+  </si>
+  <si>
+    <t>Domaine Guy Bocard</t>
+  </si>
+  <si>
+    <t>Domaine Remi Jobard</t>
+  </si>
+  <si>
+    <t>Bourgogne "Les Dressoles"</t>
+  </si>
+  <si>
+    <t>Domaine Changarnier</t>
+  </si>
+  <si>
+    <t>Bourgogne Chardonnay "Les Grandes Coutures"</t>
+  </si>
+  <si>
+    <t>Xavier Monnot</t>
+  </si>
+  <si>
+    <t>Bourgogne Aligoté "Aligato" Cuvée Zen</t>
+  </si>
+  <si>
+    <t>La Soufrandiere</t>
+  </si>
+  <si>
+    <t>Bourgogne Aligote Les Cerisiers</t>
+  </si>
+  <si>
+    <t>Jeremy Recchione</t>
+  </si>
+  <si>
+    <t>Mercurey Les Vignes de Maillonge</t>
+  </si>
+  <si>
+    <t>Michel Juillot</t>
+  </si>
+  <si>
+    <t>Hautes Cotes de Nuits Blanc</t>
+  </si>
+  <si>
+    <t>Saint Véran Climat "La Bonnode" Cuvée Ovoïde Zen</t>
   </si>
   <si>
     <t/>
@@ -466,11 +532,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
@@ -521,10 +587,10 @@
         <v>143.49</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F4" s="4">
-        <v>2008.8600000000001</v>
+        <v>1434.9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -541,10 +607,10 @@
         <v>187.86</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" s="4">
-        <v>2254.32</v>
+        <v>1878.6000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -561,10 +627,10 @@
         <v>206.22</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4">
-        <v>2474.64</v>
+        <v>2062.2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -581,10 +647,10 @@
         <v>225.42</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7" s="4">
-        <v>2705.04</v>
+        <v>2254.2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -601,30 +667,310 @@
         <v>245.93</v>
       </c>
       <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1475.58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="4">
+        <v>266.35</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>266.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="4">
+        <v>277.32</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>277.32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>2023</v>
+      </c>
+      <c r="D11" s="4">
+        <v>302.43</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>302.43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4">
-        <v>2459.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="C12">
+        <v>2022</v>
+      </c>
+      <c r="D12" s="4">
+        <v>304.74</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>304.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>2023</v>
+      </c>
+      <c r="D13" s="4">
+        <v>322.68</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>322.68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>2022</v>
+      </c>
+      <c r="D14" s="4">
+        <v>343.06</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
+        <v>343.06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>2023</v>
+      </c>
+      <c r="D15" s="4">
+        <v>344.83</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4">
+        <v>344.83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16">
+        <v>2023</v>
+      </c>
+      <c r="D16" s="4">
+        <v>345.55</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>345.55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17">
+        <v>2023</v>
+      </c>
+      <c r="D17" s="4">
+        <v>346.3</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
+        <v>346.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18">
+        <v>2023</v>
+      </c>
+      <c r="D18" s="4">
+        <v>353.22</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4">
+        <v>353.22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>2023</v>
+      </c>
+      <c r="D19" s="4">
+        <v>368.94</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
+        <v>368.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20">
+        <v>2023</v>
+      </c>
+      <c r="D20" s="4">
+        <v>382.02</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
+        <v>382.02</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <v>2023</v>
+      </c>
+      <c r="D21" s="4">
+        <v>445.34</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4">
+        <v>445.34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22">
+        <v>2023</v>
+      </c>
+      <c r="D22" s="4">
+        <v>456.87</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4">
+        <v>456.87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="6">
         <v>60</v>
       </c>
-      <c r="F9" s="7">
-        <v>11902.16</v>
+      <c r="F23" s="7">
+        <v>13965.13</v>
       </c>
     </row>
   </sheetData>

--- a/analises/vinhos/cotacao-60-garrafas-borgonha-agosto-2026.xlsx
+++ b/analises/vinhos/cotacao-60-garrafas-borgonha-agosto-2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Cotação 60 garrafas" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Cotação atualizada" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
-    <t>Cotação — 60 garrafas · 19 rótulos · faixa R$ 13.000 a R$ 14.000</t>
+    <t>Cotação atualizada — 19 rótulos</t>
   </si>
   <si>
     <t>Vinho</t>
@@ -687,10 +687,10 @@
         <v>266.35</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4">
-        <v>266.35</v>
+        <v>799.0500000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -707,10 +707,10 @@
         <v>277.32</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="4">
-        <v>277.32</v>
+        <v>831.96</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -727,10 +727,10 @@
         <v>302.43</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="4">
-        <v>302.43</v>
+        <v>907.29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -747,10 +747,10 @@
         <v>304.74</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="4">
-        <v>304.74</v>
+        <v>914.22</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -767,10 +767,10 @@
         <v>322.68</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="4">
-        <v>322.68</v>
+        <v>968.04</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -787,10 +787,10 @@
         <v>343.06</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="4">
-        <v>343.06</v>
+        <v>1029.18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -807,10 +807,10 @@
         <v>344.83</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4">
-        <v>344.83</v>
+        <v>1034.49</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -827,10 +827,10 @@
         <v>345.55</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="4">
-        <v>345.55</v>
+        <v>1036.65</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>346.3</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="4">
-        <v>346.3</v>
+        <v>1038.9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -867,10 +867,10 @@
         <v>353.22</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="4">
-        <v>353.22</v>
+        <v>1059.66</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -887,10 +887,10 @@
         <v>368.94</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="4">
-        <v>368.94</v>
+        <v>1106.82</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>382.02</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" s="4">
-        <v>382.02</v>
+        <v>1146.06</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -927,10 +927,10 @@
         <v>445.34</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="4">
-        <v>445.34</v>
+        <v>1336.02</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -947,10 +947,10 @@
         <v>456.87</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="4">
-        <v>456.87</v>
+        <v>1370.6100000000001</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -967,10 +967,10 @@
         <v>37</v>
       </c>
       <c r="E23" s="6">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="F23" s="7">
-        <v>13965.13</v>
+        <v>23684.43</v>
       </c>
     </row>
   </sheetData>
